--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Terry.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Terry.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr date1904="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_C5C7868BB4DB727CEAADABB97AF6C6DD4690E717" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3251946-AE6D-4497-93B1-F64769FA3F81}"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -30,26 +36,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="15">
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Lucida Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CITS3200 Project Billed Hours Record for Zhichong Zhang(Terry)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Lucida Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
-    </r>
-  </si>
   <si>
     <t>Wk</t>
   </si>
@@ -94,18 +80,26 @@
   <si>
     <t>Understand overall project workflow and system architecture</t>
   </si>
+  <si>
+    <r>
+      <t>CITS3200 Project Billed Hours Record for Zhichong Zhang (Terry)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Lucida Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -124,357 +118,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Lucida Sans"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -622,255 +279,33 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -885,10 +320,6 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -897,7 +328,23 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -905,94 +352,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
@@ -1065,6 +433,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1386,187 +757,186 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="5.8359375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3359375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3359375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.8359375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3359375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="1"/>
-    <col min="9" max="9" width="10.6640625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6640625" style="1"/>
+    <col min="1" max="1" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="71" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.05" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="9" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="13.05" customHeight="1">
+      <c r="A3" s="13"/>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="13" customHeight="1" spans="1:9">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="16">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="17" t="e">
+      <c r="G4" s="6">
         <f>IF(I4&gt;0,I4,IF(I4=0," ","ERROR"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H4" s="1" t="e">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H4" s="1">
         <f>IF(G4&lt;&gt;"ERROR",G4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I4" s="1" t="e">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
-        <v>#VALUE!</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="16">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="17" t="e">
+      <c r="G5" s="6">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0," ","ERROR"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="1" t="e">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ",H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I5" s="1" t="e">
+        <v>2.4999999999417923</v>
+      </c>
+      <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>#VALUE!</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="16">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="16">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="17" t="e">
+      <c r="G6" s="6">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H6" s="1" t="e">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="1">
         <f t="shared" ref="H6:H30" si="2">IF(AND(G6&lt;&gt;" ",G6&lt;&gt;"ERROR",H5&lt;&gt;" ",H5&lt;&gt;"ERROR"),G6+H5," ")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I6" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>3.9999999999417923</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="17" t="str">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="G7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H7" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f>IF(AND(G7&lt;&gt;" ",G7&lt;&gt;"ERROR",H6&lt;&gt;" ",H6&lt;&gt;"ERROR"),G7+H6," ")</f>
         <v>#VALUE!</v>
       </c>
       <c r="I7" s="1">
@@ -1575,13 +945,13 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16"/>
-      <c r="G8" s="17" t="str">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="G8" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H8" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1593,13 +963,13 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-      <c r="G9" s="17" t="str">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="G9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H9" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1611,13 +981,13 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="G10" s="17" t="str">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="G10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H10" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1629,13 +999,13 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="16"/>
-      <c r="G11" s="17" t="str">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="G11" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H11" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1647,13 +1017,13 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-      <c r="G12" s="17" t="str">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="G12" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H12" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1665,13 +1035,13 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
-      <c r="G13" s="17" t="str">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="G13" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H13" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1683,13 +1053,13 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="G14" s="17" t="str">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="G14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H14" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1701,13 +1071,13 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
-      <c r="G15" s="17" t="str">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="G15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H15" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1719,13 +1089,13 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
-      <c r="G16" s="17" t="str">
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="G16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H16" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1737,13 +1107,13 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="16"/>
-      <c r="G17" s="17" t="str">
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="G17" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H17" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1755,13 +1125,13 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
-      <c r="G18" s="17" t="str">
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="G18" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H18" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1773,13 +1143,13 @@
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="16"/>
-      <c r="G19" s="17" t="str">
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="G19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H19" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1791,13 +1161,13 @@
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="16"/>
-      <c r="G20" s="17" t="str">
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5"/>
+      <c r="G20" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H20" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1809,13 +1179,13 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="16"/>
-      <c r="G21" s="17" t="str">
+      <c r="B21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="G21" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H21" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1827,13 +1197,13 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16"/>
-      <c r="G22" s="17" t="str">
+      <c r="B22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="G22" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H22" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1845,13 +1215,13 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="16"/>
-      <c r="G23" s="17" t="str">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5"/>
+      <c r="G23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H23" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1863,13 +1233,13 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="B24" s="15"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16"/>
-      <c r="G24" s="17" t="str">
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5"/>
+      <c r="G24" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H24" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1881,13 +1251,13 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="16"/>
-      <c r="G25" s="17" t="str">
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="G25" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H25" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1899,13 +1269,13 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="G26" s="17" t="str">
+      <c r="B26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="G26" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H26" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1917,13 +1287,13 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="B27" s="15"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
-      <c r="G27" s="17" t="str">
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="G27" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H27" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1935,13 +1305,13 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
-      <c r="G28" s="17" t="str">
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="G28" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H28" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1953,13 +1323,13 @@
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="B29" s="15"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="16"/>
-      <c r="G29" s="17" t="str">
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H29" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1971,13 +1341,13 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
-      <c r="G30" s="17" t="str">
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="G30" s="6" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H30" s="1" t="e">
         <f t="shared" si="2"/>
@@ -1988,62 +1358,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="15" spans="1:9">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:9" ht="15">
+      <c r="A31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="11"/>
+      <c r="F31" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="18" t="s">
+      <c r="G31" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="H31" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="18" t="s">
+      <c r="I31" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15">
+      <c r="A32" s="13"/>
+      <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I31" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:9">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11" t="s">
+      <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
       <c r="I32" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="15"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="16"/>
-      <c r="G33" s="17" t="str">
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="G33" s="6" t="str">
         <f t="shared" ref="G33:G64" si="3">IF(I33&gt;0,I33,IF(I33=0," ","ERROR"))</f>
-        <v> </v>
+        <v/>
       </c>
       <c r="H33" s="1" t="e">
         <f>IF(AND(G33&lt;&gt;" ",G33&lt;&gt;"ERROR",H30&lt;&gt;" ",H30&lt;&gt;"ERROR"),G33+H30," ")</f>
@@ -2055,13 +1425,13 @@
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="15"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16"/>
-      <c r="G34" s="17" t="str">
+      <c r="B34" s="4"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="G34" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H34" s="1" t="e">
         <f t="shared" ref="H34:H64" si="4">IF(AND(G34&lt;&gt;" ",G34&lt;&gt;"ERROR",H33&lt;&gt;" ",H33&lt;&gt;"ERROR"),G34+H33," ")</f>
@@ -2073,13 +1443,13 @@
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="15"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="16"/>
-      <c r="G35" s="17" t="str">
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5"/>
+      <c r="G35" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H35" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2091,13 +1461,13 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="15"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="16"/>
-      <c r="G36" s="17" t="str">
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="G36" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H36" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2109,13 +1479,13 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="15"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="16"/>
-      <c r="G37" s="17" t="str">
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5"/>
+      <c r="G37" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H37" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2127,13 +1497,13 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="15"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="16"/>
-      <c r="G38" s="17" t="str">
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="G38" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H38" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2145,13 +1515,13 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="15"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="16"/>
-      <c r="G39" s="17" t="str">
+      <c r="B39" s="4"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5"/>
+      <c r="G39" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H39" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2163,13 +1533,13 @@
       </c>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="15"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="16"/>
-      <c r="G40" s="17" t="str">
+      <c r="B40" s="4"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="5"/>
+      <c r="G40" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H40" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2181,13 +1551,13 @@
       </c>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="15"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="16"/>
-      <c r="G41" s="17" t="str">
+      <c r="B41" s="4"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="5"/>
+      <c r="G41" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H41" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2199,13 +1569,13 @@
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="15"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="16"/>
-      <c r="G42" s="17" t="str">
+      <c r="B42" s="4"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="5"/>
+      <c r="G42" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H42" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2217,13 +1587,13 @@
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="15"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="16"/>
-      <c r="G43" s="17" t="str">
+      <c r="B43" s="4"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="5"/>
+      <c r="G43" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H43" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2235,13 +1605,13 @@
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="15"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="16"/>
-      <c r="G44" s="17" t="str">
+      <c r="B44" s="4"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="5"/>
+      <c r="G44" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H44" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2253,13 +1623,13 @@
       </c>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="16"/>
-      <c r="G45" s="17" t="str">
+      <c r="B45" s="4"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5"/>
+      <c r="G45" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H45" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2271,13 +1641,13 @@
       </c>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="15"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="16"/>
-      <c r="G46" s="17" t="str">
+      <c r="B46" s="4"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5"/>
+      <c r="G46" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H46" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2289,13 +1659,13 @@
       </c>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="16"/>
-      <c r="G47" s="17" t="str">
+      <c r="B47" s="4"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5"/>
+      <c r="G47" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H47" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2307,13 +1677,13 @@
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="15"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="16"/>
-      <c r="G48" s="17" t="str">
+      <c r="B48" s="4"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5"/>
+      <c r="G48" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H48" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2325,13 +1695,13 @@
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="15"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="16"/>
-      <c r="G49" s="17" t="str">
+      <c r="B49" s="4"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5"/>
+      <c r="G49" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H49" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2343,13 +1713,13 @@
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="15"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="16"/>
-      <c r="G50" s="17" t="str">
+      <c r="B50" s="4"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5"/>
+      <c r="G50" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H50" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2361,13 +1731,13 @@
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="15"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="16"/>
-      <c r="G51" s="17" t="str">
+      <c r="B51" s="4"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5"/>
+      <c r="G51" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H51" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2379,13 +1749,13 @@
       </c>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="15"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="16"/>
-      <c r="G52" s="17" t="str">
+      <c r="B52" s="4"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="5"/>
+      <c r="G52" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H52" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2397,13 +1767,13 @@
       </c>
     </row>
     <row r="53" spans="2:9">
-      <c r="B53" s="15"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="16"/>
-      <c r="G53" s="17" t="str">
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="5"/>
+      <c r="G53" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H53" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2415,13 +1785,13 @@
       </c>
     </row>
     <row r="54" spans="2:9">
-      <c r="B54" s="15"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="16"/>
-      <c r="G54" s="17" t="str">
+      <c r="B54" s="4"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="5"/>
+      <c r="G54" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H54" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2433,13 +1803,13 @@
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="B55" s="15"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="16"/>
-      <c r="G55" s="17" t="str">
+      <c r="B55" s="4"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="5"/>
+      <c r="G55" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H55" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2451,13 +1821,13 @@
       </c>
     </row>
     <row r="56" spans="2:9">
-      <c r="B56" s="15"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="16"/>
-      <c r="G56" s="17" t="str">
+      <c r="B56" s="4"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="5"/>
+      <c r="G56" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H56" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2469,13 +1839,13 @@
       </c>
     </row>
     <row r="57" spans="2:9">
-      <c r="B57" s="15"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="16"/>
-      <c r="G57" s="17" t="str">
+      <c r="B57" s="4"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="5"/>
+      <c r="G57" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H57" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2487,13 +1857,13 @@
       </c>
     </row>
     <row r="58" spans="2:9">
-      <c r="B58" s="15"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="16"/>
-      <c r="G58" s="17" t="str">
+      <c r="B58" s="4"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="5"/>
+      <c r="G58" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H58" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2505,13 +1875,13 @@
       </c>
     </row>
     <row r="59" spans="2:9">
-      <c r="B59" s="15"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="16"/>
-      <c r="G59" s="17" t="str">
+      <c r="B59" s="4"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="5"/>
+      <c r="G59" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H59" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2523,10 +1893,10 @@
       </c>
     </row>
     <row r="60" spans="2:9">
-      <c r="B60" s="15"/>
-      <c r="G60" s="17" t="str">
+      <c r="B60" s="4"/>
+      <c r="G60" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H60" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2538,10 +1908,10 @@
       </c>
     </row>
     <row r="61" spans="2:9">
-      <c r="B61" s="15"/>
-      <c r="G61" s="17" t="str">
+      <c r="B61" s="4"/>
+      <c r="G61" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H61" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2553,10 +1923,10 @@
       </c>
     </row>
     <row r="62" spans="2:9">
-      <c r="B62" s="15"/>
-      <c r="G62" s="17" t="str">
+      <c r="B62" s="4"/>
+      <c r="G62" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H62" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2568,10 +1938,10 @@
       </c>
     </row>
     <row r="63" spans="2:9">
-      <c r="B63" s="15"/>
-      <c r="G63" s="17" t="str">
+      <c r="B63" s="4"/>
+      <c r="G63" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H63" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2583,10 +1953,10 @@
       </c>
     </row>
     <row r="64" spans="2:9">
-      <c r="B64" s="15"/>
-      <c r="G64" s="17" t="str">
+      <c r="B64" s="4"/>
+      <c r="G64" s="6" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H64" s="1" t="e">
         <f t="shared" si="4"/>
@@ -2597,58 +1967,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="15" spans="1:9">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="1:9" ht="15">
+      <c r="A65" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="6" t="s">
+      <c r="E65" s="11"/>
+      <c r="F65" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="18" t="s">
+      <c r="G65" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G65" s="18" t="s">
+      <c r="H65" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="I65" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15">
+      <c r="A66" s="13"/>
+      <c r="B66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" ht="15" spans="1:9">
-      <c r="A66" s="10"/>
-      <c r="B66" s="11" t="s">
+      <c r="C66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
       <c r="I66" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="G67" s="17" t="str">
+      <c r="G67" s="6" t="str">
         <f t="shared" ref="G67:G98" si="5">IF(I67&gt;0,I67,IF(I67=0," ","ERROR"))</f>
-        <v> </v>
+        <v/>
       </c>
       <c r="H67" s="1" t="e">
         <f>IF(AND(G67&lt;&gt;" ",G67&lt;&gt;"ERROR",H64&lt;&gt;" ",H64&lt;&gt;"ERROR"),G67+H64," ")</f>
@@ -2660,9 +2030,9 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="G68" s="17" t="str">
+      <c r="G68" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H68" s="1" t="e">
         <f t="shared" ref="H68:H98" si="6">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ",H67&lt;&gt;"ERROR"),G68+H67," ")</f>
@@ -2674,9 +2044,9 @@
       </c>
     </row>
     <row r="69" spans="1:9">
-      <c r="G69" s="17" t="str">
+      <c r="G69" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H69" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2688,9 +2058,9 @@
       </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="G70" s="17" t="str">
+      <c r="G70" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H70" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2702,9 +2072,9 @@
       </c>
     </row>
     <row r="71" spans="1:9">
-      <c r="G71" s="17" t="str">
+      <c r="G71" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H71" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2716,9 +2086,9 @@
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="G72" s="17" t="str">
+      <c r="G72" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H72" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2730,9 +2100,9 @@
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="G73" s="17" t="str">
+      <c r="G73" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H73" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2744,9 +2114,9 @@
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="G74" s="17" t="str">
+      <c r="G74" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H74" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2758,9 +2128,9 @@
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="G75" s="17" t="str">
+      <c r="G75" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H75" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2772,9 +2142,9 @@
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="G76" s="17" t="str">
+      <c r="G76" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H76" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2786,9 +2156,9 @@
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="G77" s="17" t="str">
+      <c r="G77" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H77" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2800,9 +2170,9 @@
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="G78" s="17" t="str">
+      <c r="G78" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H78" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2814,9 +2184,9 @@
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="G79" s="17" t="str">
+      <c r="G79" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H79" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2828,9 +2198,9 @@
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="G80" s="17" t="str">
+      <c r="G80" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H80" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2842,9 +2212,9 @@
       </c>
     </row>
     <row r="81" spans="7:9">
-      <c r="G81" s="17" t="str">
+      <c r="G81" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H81" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2856,9 +2226,9 @@
       </c>
     </row>
     <row r="82" spans="7:9">
-      <c r="G82" s="17" t="str">
+      <c r="G82" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H82" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2870,9 +2240,9 @@
       </c>
     </row>
     <row r="83" spans="7:9">
-      <c r="G83" s="17" t="str">
+      <c r="G83" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H83" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2884,9 +2254,9 @@
       </c>
     </row>
     <row r="84" spans="7:9">
-      <c r="G84" s="17" t="str">
+      <c r="G84" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H84" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2898,9 +2268,9 @@
       </c>
     </row>
     <row r="85" spans="7:9">
-      <c r="G85" s="17" t="str">
+      <c r="G85" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H85" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2912,9 +2282,9 @@
       </c>
     </row>
     <row r="86" spans="7:9">
-      <c r="G86" s="17" t="str">
+      <c r="G86" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H86" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2926,9 +2296,9 @@
       </c>
     </row>
     <row r="87" spans="7:9">
-      <c r="G87" s="17" t="str">
+      <c r="G87" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H87" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2940,9 +2310,9 @@
       </c>
     </row>
     <row r="88" spans="7:9">
-      <c r="G88" s="17" t="str">
+      <c r="G88" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H88" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2954,9 +2324,9 @@
       </c>
     </row>
     <row r="89" spans="7:9">
-      <c r="G89" s="17" t="str">
+      <c r="G89" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H89" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2968,9 +2338,9 @@
       </c>
     </row>
     <row r="90" spans="7:9">
-      <c r="G90" s="17" t="str">
+      <c r="G90" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H90" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2982,9 +2352,9 @@
       </c>
     </row>
     <row r="91" spans="7:9">
-      <c r="G91" s="17" t="str">
+      <c r="G91" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H91" s="1" t="e">
         <f t="shared" si="6"/>
@@ -2996,9 +2366,9 @@
       </c>
     </row>
     <row r="92" spans="7:9">
-      <c r="G92" s="17" t="str">
+      <c r="G92" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H92" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3010,9 +2380,9 @@
       </c>
     </row>
     <row r="93" spans="7:9">
-      <c r="G93" s="17" t="str">
+      <c r="G93" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H93" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3024,9 +2394,9 @@
       </c>
     </row>
     <row r="94" spans="7:9">
-      <c r="G94" s="17" t="str">
+      <c r="G94" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H94" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3038,9 +2408,9 @@
       </c>
     </row>
     <row r="95" spans="7:9">
-      <c r="G95" s="17" t="str">
+      <c r="G95" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H95" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3052,9 +2422,9 @@
       </c>
     </row>
     <row r="96" spans="7:9">
-      <c r="G96" s="17" t="str">
+      <c r="G96" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H96" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3066,9 +2436,9 @@
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="G97" s="17" t="str">
+      <c r="G97" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H97" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3080,9 +2450,9 @@
       </c>
     </row>
     <row r="98" spans="1:9">
-      <c r="G98" s="17" t="str">
+      <c r="G98" s="6" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H98" s="1" t="e">
         <f t="shared" si="6"/>
@@ -3093,58 +2463,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" ht="15" spans="1:9">
-      <c r="A99" s="5" t="s">
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="6" t="s">
+      <c r="E99" s="11"/>
+      <c r="F99" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="18" t="s">
+      <c r="G99" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G99" s="18" t="s">
+      <c r="H99" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H99" s="18" t="s">
+      <c r="I99" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" s="13"/>
+      <c r="B100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I99" s="1" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="100" ht="15" spans="1:9">
-      <c r="A100" s="10"/>
-      <c r="B100" s="11" t="s">
+      <c r="C100" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="11" t="s">
+      <c r="D100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="18"/>
-      <c r="G100" s="18"/>
-      <c r="H100" s="18"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
       <c r="I100" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="G101" s="17" t="str">
+      <c r="G101" s="6" t="str">
         <f t="shared" ref="G101:G132" si="8">IF(I101&gt;0,I101,IF(I101=0," ","ERROR"))</f>
-        <v> </v>
+        <v/>
       </c>
       <c r="H101" s="1" t="e">
         <f>IF(AND(G101&lt;&gt;" ",G101&lt;&gt;"ERROR",H98&lt;&gt;" ",H98&lt;&gt;"ERROR"),G101+H98," ")</f>
@@ -3156,9 +2526,9 @@
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="G102" s="17" t="str">
+      <c r="G102" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H102" s="1" t="e">
         <f t="shared" ref="H102:H132" si="9">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ",H101&lt;&gt;"ERROR"),G102+H101," ")</f>
@@ -3170,9 +2540,9 @@
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="G103" s="17" t="str">
+      <c r="G103" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H103" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3184,9 +2554,9 @@
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="G104" s="17" t="str">
+      <c r="G104" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H104" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3198,9 +2568,9 @@
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="G105" s="17" t="str">
+      <c r="G105" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H105" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3212,9 +2582,9 @@
       </c>
     </row>
     <row r="106" spans="1:9">
-      <c r="G106" s="17" t="str">
+      <c r="G106" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H106" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3226,9 +2596,9 @@
       </c>
     </row>
     <row r="107" spans="1:9">
-      <c r="G107" s="17" t="str">
+      <c r="G107" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H107" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3240,9 +2610,9 @@
       </c>
     </row>
     <row r="108" spans="1:9">
-      <c r="G108" s="17" t="str">
+      <c r="G108" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H108" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3254,9 +2624,9 @@
       </c>
     </row>
     <row r="109" spans="1:9">
-      <c r="G109" s="17" t="str">
+      <c r="G109" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H109" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3268,9 +2638,9 @@
       </c>
     </row>
     <row r="110" spans="1:9">
-      <c r="G110" s="17" t="str">
+      <c r="G110" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H110" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3282,9 +2652,9 @@
       </c>
     </row>
     <row r="111" spans="1:9">
-      <c r="G111" s="17" t="str">
+      <c r="G111" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H111" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3296,9 +2666,9 @@
       </c>
     </row>
     <row r="112" spans="1:9">
-      <c r="G112" s="17" t="str">
+      <c r="G112" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H112" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3310,9 +2680,9 @@
       </c>
     </row>
     <row r="113" spans="7:9">
-      <c r="G113" s="17" t="str">
+      <c r="G113" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H113" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3324,9 +2694,9 @@
       </c>
     </row>
     <row r="114" spans="7:9">
-      <c r="G114" s="17" t="str">
+      <c r="G114" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H114" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3338,9 +2708,9 @@
       </c>
     </row>
     <row r="115" spans="7:9">
-      <c r="G115" s="17" t="str">
+      <c r="G115" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H115" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3352,9 +2722,9 @@
       </c>
     </row>
     <row r="116" spans="7:9">
-      <c r="G116" s="17" t="str">
+      <c r="G116" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H116" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3366,9 +2736,9 @@
       </c>
     </row>
     <row r="117" spans="7:9">
-      <c r="G117" s="17" t="str">
+      <c r="G117" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H117" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3380,9 +2750,9 @@
       </c>
     </row>
     <row r="118" spans="7:9">
-      <c r="G118" s="17" t="str">
+      <c r="G118" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H118" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3394,9 +2764,9 @@
       </c>
     </row>
     <row r="119" spans="7:9">
-      <c r="G119" s="17" t="str">
+      <c r="G119" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H119" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3408,9 +2778,9 @@
       </c>
     </row>
     <row r="120" spans="7:9">
-      <c r="G120" s="17" t="str">
+      <c r="G120" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H120" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3422,9 +2792,9 @@
       </c>
     </row>
     <row r="121" spans="7:9">
-      <c r="G121" s="17" t="str">
+      <c r="G121" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H121" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3436,9 +2806,9 @@
       </c>
     </row>
     <row r="122" spans="7:9">
-      <c r="G122" s="17" t="str">
+      <c r="G122" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H122" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3450,9 +2820,9 @@
       </c>
     </row>
     <row r="123" spans="7:9">
-      <c r="G123" s="17" t="str">
+      <c r="G123" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H123" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3464,9 +2834,9 @@
       </c>
     </row>
     <row r="124" spans="7:9">
-      <c r="G124" s="17" t="str">
+      <c r="G124" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H124" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3478,9 +2848,9 @@
       </c>
     </row>
     <row r="125" spans="7:9">
-      <c r="G125" s="17" t="str">
+      <c r="G125" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H125" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3492,9 +2862,9 @@
       </c>
     </row>
     <row r="126" spans="7:9">
-      <c r="G126" s="17" t="str">
+      <c r="G126" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H126" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3506,9 +2876,9 @@
       </c>
     </row>
     <row r="127" spans="7:9">
-      <c r="G127" s="17" t="str">
+      <c r="G127" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H127" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3520,9 +2890,9 @@
       </c>
     </row>
     <row r="128" spans="7:9">
-      <c r="G128" s="17" t="str">
+      <c r="G128" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H128" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3534,9 +2904,9 @@
       </c>
     </row>
     <row r="129" spans="7:9">
-      <c r="G129" s="17" t="str">
+      <c r="G129" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H129" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3548,9 +2918,9 @@
       </c>
     </row>
     <row r="130" spans="7:9">
-      <c r="G130" s="17" t="str">
+      <c r="G130" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H130" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3562,9 +2932,9 @@
       </c>
     </row>
     <row r="131" spans="7:9">
-      <c r="G131" s="17" t="str">
+      <c r="G131" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H131" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3576,9 +2946,9 @@
       </c>
     </row>
     <row r="132" spans="7:9">
-      <c r="G132" s="17" t="str">
+      <c r="G132" s="6" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
+        <v/>
       </c>
       <c r="H132" s="1" t="e">
         <f t="shared" si="9"/>
@@ -3591,11 +2961,14 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="G99:G100"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="D65:E65"/>
     <mergeCell ref="B99:C99"/>
@@ -3604,30 +2977,26 @@
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F31:F32"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="G99:G100"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H99:H100"/>
   </mergeCells>
-  <pageMargins left="0.748031496062992" right="0.748031496062992" top="0.984251968503937" bottom="0.984251968503937" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.74803149606299202" right="0.74803149606299202" top="0.98425196850393704" bottom="0.98425196850393704" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3636,10 +3005,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
